--- a/accessories/cable-5/cable-5.xlsx
+++ b/accessories/cable-5/cable-5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Battery-Lab-Hardware\accessories\cable-5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A27FCA7C-9D80-45C4-9234-73C9A83FDE8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95A4293A-B9B1-462D-AAD8-412DCD3847F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3090" windowWidth="21600" windowHeight="11295" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="77">
   <si>
     <t>Individual Cost</t>
   </si>
@@ -258,6 +258,15 @@
   </si>
   <si>
     <t>TERM BLADE FEMALE 14-18AWG SILV</t>
+  </si>
+  <si>
+    <t>Main Female Housing</t>
+  </si>
+  <si>
+    <t>A32500-0009</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/anderson-power-products-inc/A32500-0009/14833308?s=N4IgTCBcDaIIIGYwFYAMqC07UE4QF0BfIA</t>
   </si>
 </sst>
 </file>
@@ -866,27 +875,27 @@
       <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="23">
         <v>1</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="24">
         <v>19.18</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="24">
         <f>D3*E3</f>
         <v>19.18</v>
       </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="1" t="s">
+      <c r="G3" s="25"/>
+      <c r="H3" s="26" t="s">
         <v>15</v>
       </c>
       <c r="I3" s="1"/>
@@ -1176,7 +1185,7 @@
         <v>72.62</v>
       </c>
       <c r="F14" s="9">
-        <f t="shared" ref="F14:F17" si="3">D14*E14</f>
+        <f t="shared" ref="F14:F18" si="3">D14*E14</f>
         <v>72.62</v>
       </c>
       <c r="G14" s="5"/>
@@ -1264,14 +1273,29 @@
       <c r="I17" s="4"/>
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="10"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="9"/>
+      <c r="A18" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="2">
+        <v>1</v>
+      </c>
+      <c r="E18" s="8">
+        <v>23.22</v>
+      </c>
+      <c r="F18" s="9">
+        <f t="shared" si="3"/>
+        <v>23.22</v>
+      </c>
       <c r="G18" s="5"/>
-      <c r="H18" s="3"/>
+      <c r="H18" s="3" t="s">
+        <v>76</v>
+      </c>
       <c r="I18" s="4"/>
     </row>
     <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1317,7 +1341,7 @@
       </c>
       <c r="F23" s="5">
         <f>SUM(F2:F22)</f>
-        <v>460.21999999999997</v>
+        <v>483.43999999999994</v>
       </c>
     </row>
   </sheetData>
@@ -1341,8 +1365,9 @@
     <hyperlink ref="H9" r:id="rId16" xr:uid="{0BF14A02-DB2B-44C8-ADFD-F6B888D0D1E2}"/>
     <hyperlink ref="H5" r:id="rId17" xr:uid="{D098FC55-60BA-44A1-88B5-F7A95F7F2234}"/>
     <hyperlink ref="H8" r:id="rId18" xr:uid="{E4B64C1A-2E26-4C6F-9252-C15670A96A6B}"/>
+    <hyperlink ref="H18" r:id="rId19" xr:uid="{BC482846-CA0B-4C8C-A6F1-3CDFDF09F63D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId19"/>
+  <pageSetup orientation="portrait" r:id="rId20"/>
 </worksheet>
 </file>
--- a/accessories/cable-5/cable-5.xlsx
+++ b/accessories/cable-5/cable-5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Battery-Lab-Hardware\accessories\cable-5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/austindowney/Documents/GitHub/Battery-Lab-Hardware/accessories/cable-5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95A4293A-B9B1-462D-AAD8-412DCD3847F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FEFB595-409F-2041-94D9-268BDB455A43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="68">
   <si>
     <t>Individual Cost</t>
   </si>
@@ -83,39 +83,18 @@
     <t>https://www.digikey.com/en/products/detail/anderson-power-products-inc/320-1150/10650211</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/anderson-power-products-inc/E32500-0009/14551095?utm_source=oemsecrets&amp;utm_medium=aggregator&amp;utm_campaign=buynow</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/anderson-power-products-inc/A320HL-MK/14552019?utm_source=oemsecrets&amp;utm_medium=aggregator&amp;utm_campaign=buynow</t>
-  </si>
-  <si>
-    <t>EBC 320-2 Term Blade Female</t>
-  </si>
-  <si>
-    <t>E32500-0009 (Connector)</t>
-  </si>
-  <si>
     <t>A320H (Connector handle)</t>
   </si>
   <si>
     <t>TERM BLADE FEMALE 1/0AWG SILVER</t>
   </si>
   <si>
-    <t>E32500-0009</t>
-  </si>
-  <si>
-    <t>A320HL-MK</t>
-  </si>
-  <si>
     <t>320-1150</t>
   </si>
   <si>
     <t>CONN RCPT HSG 2POS</t>
   </si>
   <si>
-    <t>DIN LATCH HANDLE/LEVER/ HDW</t>
-  </si>
-  <si>
     <t>https://www.digikey.com/en/products/detail/anderson-power-products-inc/E320-35/14550315?s=N4IgTCBcDaIKIGYwAYC0CCsIC6BfIA</t>
   </si>
   <si>
@@ -125,21 +104,9 @@
     <t xml:space="preserve"> EBC 320 Upper Auxiliary Contact</t>
   </si>
   <si>
-    <t xml:space="preserve"> EBC 320 Lower Auxiliary Contact</t>
-  </si>
-  <si>
     <t>E320-35</t>
   </si>
   <si>
-    <t>160-13</t>
-  </si>
-  <si>
-    <t>160/320 LOW PIL/AUX SOCK 6MM</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/anderson-power-products-inc/160-13/10650230</t>
-  </si>
-  <si>
     <t>8 AWG main contact</t>
   </si>
   <si>
@@ -254,9 +221,6 @@
     <t>320-25</t>
   </si>
   <si>
-    <t>???  EBC 320 Lower Auxiliary Contact</t>
-  </si>
-  <si>
     <t>TERM BLADE FEMALE 14-18AWG SILV</t>
   </si>
   <si>
@@ -267,6 +231,15 @@
   </si>
   <si>
     <t>https://www.digikey.com/en/products/detail/anderson-power-products-inc/A32500-0009/14833308?s=N4IgTCBcDaIIIGYwFYAMqC07UE4QF0BfIA</t>
+  </si>
+  <si>
+    <t>Large Power Contacts</t>
+  </si>
+  <si>
+    <t>Larger Auxiliary Contact</t>
+  </si>
+  <si>
+    <t>Smaller Auxiliary Contact</t>
   </si>
 </sst>
 </file>
@@ -279,7 +252,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -326,23 +299,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <strike/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <strike/>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -376,7 +332,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -431,23 +387,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="7" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -789,25 +728,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
-  <dimension ref="A1:M23"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.28515625" customWidth="1"/>
-    <col min="2" max="2" width="37.85546875" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.33203125" customWidth="1"/>
+    <col min="2" max="2" width="37.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="79" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="45.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="83.5703125" customWidth="1"/>
-    <col min="11" max="11" width="62.5703125" customWidth="1"/>
-    <col min="12" max="12" width="55.85546875" customWidth="1"/>
+    <col min="9" max="9" width="45.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="83.5" customWidth="1"/>
+    <col min="11" max="11" width="62.5" customWidth="1"/>
+    <col min="12" max="12" width="55.83203125" customWidth="1"/>
     <col min="13" max="13" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>10</v>
       </c>
@@ -848,15 +787,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>23</v>
       </c>
       <c r="D2" s="19">
         <v>2</v>
@@ -874,500 +813,417 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="23" t="s">
+    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="19">
+        <v>1</v>
+      </c>
+      <c r="E3" s="9">
+        <v>8.51</v>
+      </c>
+      <c r="F3" s="9">
+        <f>D3*E3</f>
+        <v>8.51</v>
+      </c>
+      <c r="G3" s="5"/>
+      <c r="H3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="23">
-        <v>1</v>
-      </c>
-      <c r="E3" s="24">
-        <v>19.18</v>
-      </c>
-      <c r="F3" s="24">
-        <f>D3*E3</f>
-        <v>19.18</v>
-      </c>
-      <c r="G3" s="25"/>
-      <c r="H3" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="1"/>
-    </row>
-    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="27" t="s">
+      <c r="B4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="19">
+        <v>2</v>
+      </c>
+      <c r="E4" s="9">
+        <v>11.21</v>
+      </c>
+      <c r="F4" s="9">
+        <f t="shared" ref="F4:F6" si="0">D4*E4</f>
+        <v>22.42</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="23">
-        <v>1</v>
-      </c>
-      <c r="E4" s="24">
-        <v>33.840000000000003</v>
-      </c>
-      <c r="F4" s="24">
-        <f>D4*E4</f>
-        <v>33.840000000000003</v>
-      </c>
-      <c r="G4" s="25"/>
-      <c r="H4" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="1"/>
-    </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>68</v>
+      <c r="I4" s="4"/>
+    </row>
+    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>61</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D5" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" s="9">
-        <v>8.51</v>
+        <v>11.25</v>
       </c>
       <c r="F5" s="9">
-        <f>D5*E5</f>
-        <v>8.51</v>
+        <f t="shared" ref="F5" si="1">D5*E5</f>
+        <v>22.5</v>
       </c>
       <c r="G5" s="5"/>
-      <c r="H5" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H5" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="I5" s="4"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+    </row>
+    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
+        <v>66</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>54</v>
       </c>
       <c r="D6" s="19">
         <v>2</v>
       </c>
       <c r="E6" s="9">
-        <v>11.21</v>
+        <v>14</v>
       </c>
       <c r="F6" s="9">
-        <f t="shared" ref="F6:F9" si="0">D6*E6</f>
-        <v>22.42</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" s="4"/>
-    </row>
-    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="23">
-        <v>2</v>
-      </c>
-      <c r="E7" s="24">
-        <v>12.44</v>
-      </c>
-      <c r="F7" s="24">
-        <f t="shared" si="0"/>
-        <v>24.88</v>
-      </c>
-      <c r="G7" s="25"/>
-      <c r="H7" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="I7" s="4"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-    </row>
-    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>72</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" s="19">
-        <v>2</v>
-      </c>
-      <c r="E8" s="9">
-        <v>11.25</v>
-      </c>
-      <c r="F8" s="9">
-        <f t="shared" ref="F8" si="1">D8*E8</f>
-        <v>22.5</v>
-      </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="I8" s="4"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" s="19">
-        <v>2</v>
-      </c>
-      <c r="E9" s="9">
-        <v>14</v>
-      </c>
-      <c r="F9" s="9">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
+      <c r="G6" s="5"/>
+      <c r="H6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I6" s="4"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+    </row>
+    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="2">
+        <v>2</v>
+      </c>
+      <c r="E7" s="9">
+        <v>2.72</v>
+      </c>
+      <c r="F7" s="9">
+        <f>E7*D7</f>
+        <v>5.44</v>
+      </c>
+      <c r="G7" s="5"/>
+      <c r="H7" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="9">
+        <v>12.54</v>
+      </c>
+      <c r="F8" s="9">
+        <f t="shared" ref="F8:F10" si="2">E8*D8</f>
+        <v>12.54</v>
+      </c>
+      <c r="G8" s="5"/>
+      <c r="H8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="9">
+        <v>12.54</v>
+      </c>
+      <c r="F9" s="9">
+        <f t="shared" si="2"/>
+        <v>12.54</v>
+      </c>
       <c r="G9" s="5"/>
       <c r="H9" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="I9" s="4"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>34</v>
       </c>
+    </row>
+    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="10" t="s">
+        <v>35</v>
+      </c>
       <c r="B10" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D10" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="9">
-        <v>2.72</v>
+        <v>128.19</v>
       </c>
       <c r="F10" s="9">
-        <f>E10*D10</f>
-        <v>5.44</v>
+        <f t="shared" si="2"/>
+        <v>128.19</v>
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="I10" s="4"/>
+    </row>
+    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="20" t="s">
         <v>40</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>41</v>
       </c>
       <c r="D11" s="2">
         <v>1</v>
       </c>
       <c r="E11" s="9">
-        <v>12.54</v>
+        <v>72.62</v>
       </c>
       <c r="F11" s="9">
-        <f t="shared" ref="F11:F13" si="2">E11*D11</f>
-        <v>12.54</v>
+        <f t="shared" ref="F11:F15" si="3">D11*E11</f>
+        <v>72.62</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I11" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I11" s="4"/>
+    </row>
+    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="20" t="s">
         <v>44</v>
       </c>
+      <c r="C12" s="20">
+        <v>191930200</v>
+      </c>
       <c r="D12" s="2">
+        <v>2</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="F12" s="9">
+        <f t="shared" si="3"/>
         <v>1</v>
-      </c>
-      <c r="E12" s="9">
-        <v>12.54</v>
-      </c>
-      <c r="F12" s="9">
-        <f t="shared" si="2"/>
-        <v>12.54</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I12" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I12" s="4"/>
+    </row>
+    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>46</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C13" s="20" t="s">
-        <v>48</v>
+      <c r="C13" s="16">
+        <v>191930089</v>
       </c>
       <c r="D13" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" s="9">
-        <v>128.19</v>
+        <v>0.42</v>
       </c>
       <c r="F13" s="9">
-        <f t="shared" si="2"/>
-        <v>128.19</v>
+        <f t="shared" si="3"/>
+        <v>0.84</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I13" s="4"/>
+    </row>
+    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="I13" s="4"/>
-    </row>
-    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+      <c r="B14" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="20" t="s">
         <v>51</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>52</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
       </c>
       <c r="E14" s="9">
-        <v>72.62</v>
+        <v>6.22</v>
       </c>
       <c r="F14" s="9">
-        <f t="shared" ref="F14:F18" si="3">D14*E14</f>
-        <v>72.62</v>
+        <f t="shared" si="3"/>
+        <v>6.22</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" s="20">
-        <v>191930200</v>
+        <v>18</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="D15" s="2">
-        <v>2</v>
-      </c>
-      <c r="E15" s="9">
-        <v>0.5</v>
+        <v>1</v>
+      </c>
+      <c r="E15" s="8">
+        <v>23.22</v>
       </c>
       <c r="F15" s="9">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>23.22</v>
       </c>
       <c r="G15" s="5"/>
-      <c r="H15" s="1" t="s">
-        <v>56</v>
+      <c r="H15" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="I15" s="4"/>
     </row>
-    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C16" s="16">
-        <v>191930089</v>
-      </c>
-      <c r="D16" s="2">
-        <v>2</v>
-      </c>
-      <c r="E16" s="9">
-        <v>0.42</v>
-      </c>
-      <c r="F16" s="9">
-        <f t="shared" si="3"/>
-        <v>0.84</v>
-      </c>
-      <c r="G16" s="5"/>
-      <c r="H16" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="I16" s="4"/>
-    </row>
-    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="D17" s="2">
-        <v>1</v>
-      </c>
-      <c r="E17" s="9">
-        <v>6.22</v>
-      </c>
-      <c r="F17" s="9">
-        <f t="shared" si="3"/>
-        <v>6.22</v>
-      </c>
-      <c r="G17" s="5"/>
-      <c r="H17" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I17" s="4"/>
-    </row>
-    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D18" s="2">
-        <v>1</v>
-      </c>
-      <c r="E18" s="8">
-        <v>23.22</v>
-      </c>
-      <c r="F18" s="9">
-        <f t="shared" si="3"/>
-        <v>23.22</v>
-      </c>
-      <c r="G18" s="5"/>
-      <c r="H18" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I18" s="4"/>
-    </row>
-    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-    </row>
-    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="11"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-    </row>
-    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E23" s="7" t="s">
+    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+    </row>
+    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+    </row>
+    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E20" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F23" s="5">
-        <f>SUM(F2:F22)</f>
-        <v>483.43999999999994</v>
+      <c r="F20" s="5">
+        <f>SUM(F2:F19)</f>
+        <v>405.53999999999996</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1" xr:uid="{47569AE6-6AA0-4875-B93F-ACB3A5943EC4}"/>
-    <hyperlink ref="H3" r:id="rId2" xr:uid="{FCB99C6E-4A13-451F-A9C9-4E80B9322403}"/>
-    <hyperlink ref="H4" r:id="rId3" xr:uid="{FF2B4745-4047-4C27-BB02-026AF58F36BA}"/>
-    <hyperlink ref="H6" r:id="rId4" xr:uid="{C0E6E945-7E03-425E-862B-42F2D3A430D7}"/>
-    <hyperlink ref="H7" r:id="rId5" xr:uid="{A8116950-CB98-4C59-8274-DB9EC6FD4DDE}"/>
-    <hyperlink ref="H13" r:id="rId6" xr:uid="{29C65987-503D-4D38-A3A8-F300B92B5979}"/>
-    <hyperlink ref="H10" r:id="rId7" xr:uid="{D49830EC-B643-4C9C-A66A-316B6E8D393B}"/>
-    <hyperlink ref="H11" r:id="rId8" xr:uid="{DB6CFF9E-0CFE-4630-97DC-2259E72BBA6B}"/>
-    <hyperlink ref="H12" r:id="rId9" xr:uid="{7F0A5667-B170-4E9F-A116-7812C5481D5D}"/>
-    <hyperlink ref="I11" r:id="rId10" xr:uid="{47AB98CE-DF5D-4668-ABC4-20DA7A425CBD}"/>
-    <hyperlink ref="I12" r:id="rId11" xr:uid="{FE305D2A-720D-4EAC-A689-433507294DC8}"/>
-    <hyperlink ref="H14" r:id="rId12" xr:uid="{4AF02486-862F-4C90-B472-12C65FB0F86D}"/>
-    <hyperlink ref="H15" r:id="rId13" xr:uid="{60DC3860-834C-416B-A80D-912D2A7218E7}"/>
-    <hyperlink ref="H16" r:id="rId14" xr:uid="{DEEF517E-6B30-41FE-90B5-BDD5F67AF727}"/>
-    <hyperlink ref="H17" r:id="rId15" xr:uid="{F28C2672-213B-4C58-924E-5743A03E60B9}"/>
-    <hyperlink ref="H9" r:id="rId16" xr:uid="{0BF14A02-DB2B-44C8-ADFD-F6B888D0D1E2}"/>
-    <hyperlink ref="H5" r:id="rId17" xr:uid="{D098FC55-60BA-44A1-88B5-F7A95F7F2234}"/>
-    <hyperlink ref="H8" r:id="rId18" xr:uid="{E4B64C1A-2E26-4C6F-9252-C15670A96A6B}"/>
-    <hyperlink ref="H18" r:id="rId19" xr:uid="{BC482846-CA0B-4C8C-A6F1-3CDFDF09F63D}"/>
+    <hyperlink ref="H4" r:id="rId2" xr:uid="{C0E6E945-7E03-425E-862B-42F2D3A430D7}"/>
+    <hyperlink ref="H10" r:id="rId3" xr:uid="{29C65987-503D-4D38-A3A8-F300B92B5979}"/>
+    <hyperlink ref="H7" r:id="rId4" xr:uid="{D49830EC-B643-4C9C-A66A-316B6E8D393B}"/>
+    <hyperlink ref="H8" r:id="rId5" xr:uid="{DB6CFF9E-0CFE-4630-97DC-2259E72BBA6B}"/>
+    <hyperlink ref="H9" r:id="rId6" xr:uid="{7F0A5667-B170-4E9F-A116-7812C5481D5D}"/>
+    <hyperlink ref="I8" r:id="rId7" xr:uid="{47AB98CE-DF5D-4668-ABC4-20DA7A425CBD}"/>
+    <hyperlink ref="I9" r:id="rId8" xr:uid="{FE305D2A-720D-4EAC-A689-433507294DC8}"/>
+    <hyperlink ref="H11" r:id="rId9" xr:uid="{4AF02486-862F-4C90-B472-12C65FB0F86D}"/>
+    <hyperlink ref="H12" r:id="rId10" xr:uid="{60DC3860-834C-416B-A80D-912D2A7218E7}"/>
+    <hyperlink ref="H13" r:id="rId11" xr:uid="{DEEF517E-6B30-41FE-90B5-BDD5F67AF727}"/>
+    <hyperlink ref="H14" r:id="rId12" xr:uid="{F28C2672-213B-4C58-924E-5743A03E60B9}"/>
+    <hyperlink ref="H6" r:id="rId13" xr:uid="{0BF14A02-DB2B-44C8-ADFD-F6B888D0D1E2}"/>
+    <hyperlink ref="H3" r:id="rId14" xr:uid="{D098FC55-60BA-44A1-88B5-F7A95F7F2234}"/>
+    <hyperlink ref="H5" r:id="rId15" xr:uid="{E4B64C1A-2E26-4C6F-9252-C15670A96A6B}"/>
+    <hyperlink ref="H15" r:id="rId16" xr:uid="{BC482846-CA0B-4C8C-A6F1-3CDFDF09F63D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId20"/>
+  <pageSetup orientation="portrait" r:id="rId17"/>
 </worksheet>
 </file>
--- a/accessories/cable-5/cable-5.xlsx
+++ b/accessories/cable-5/cable-5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/austindowney/Documents/GitHub/Battery-Lab-Hardware/accessories/cable-5/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Battery-Lab-Hardware\accessories\cable-5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FEFB595-409F-2041-94D9-268BDB455A43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A797BD0-3845-4126-BB8E-2335E24DF764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-16320" yWindow="-12765" windowWidth="16440" windowHeight="28320" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="78">
   <si>
     <t>Individual Cost</t>
   </si>
@@ -95,18 +95,6 @@
     <t>CONN RCPT HSG 2POS</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/anderson-power-products-inc/E320-35/14550315?s=N4IgTCBcDaIKIGYwAYC0CCsIC6BfIA</t>
-  </si>
-  <si>
-    <t>4.0MM AUXILIARY SOCKET</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> EBC 320 Upper Auxiliary Contact</t>
-  </si>
-  <si>
-    <t>E320-35</t>
-  </si>
-  <si>
     <t>8 AWG main contact</t>
   </si>
   <si>
@@ -240,6 +228,48 @@
   </si>
   <si>
     <t>Smaller Auxiliary Contact</t>
+  </si>
+  <si>
+    <t>https://www.grainger.com/product/QUICKCABLE-Heat-Shrink-Tubing-0-75-in-64TX48</t>
+  </si>
+  <si>
+    <t>Primary or Alternative Part</t>
+  </si>
+  <si>
+    <t>Primary</t>
+  </si>
+  <si>
+    <t>Alternative</t>
+  </si>
+  <si>
+    <t>QUICKCABLE Heat Shrink Tubing: 0.75 in I.D. Before Shrinking, 0.25 in I.D. After Shrinking, 5 PK</t>
+  </si>
+  <si>
+    <t>5662-005B</t>
+  </si>
+  <si>
+    <t>Precut to 6" which can be nice</t>
+  </si>
+  <si>
+    <t>8 AWG Red Wire</t>
+  </si>
+  <si>
+    <t>8 AWG Black Wire</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/cnc-tech/3132-8-1-0100-004-1-TS/25587759</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/cnc-tech/3132-8-1-0100-001-1-TS/25587757</t>
+  </si>
+  <si>
+    <t>3132-8-1-0100-001-1-TS</t>
+  </si>
+  <si>
+    <t>3132-8-1-0100-004-1-TS</t>
+  </si>
+  <si>
+    <t>UL3132, SILICONE WIRE, 8AWG, RED</t>
   </si>
 </sst>
 </file>
@@ -728,502 +758,612 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
-  <dimension ref="A1:M20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:N22"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.33203125" customWidth="1"/>
-    <col min="2" max="2" width="37.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="79" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="45.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="83.5" customWidth="1"/>
-    <col min="11" max="11" width="62.5" customWidth="1"/>
-    <col min="12" max="12" width="55.83203125" customWidth="1"/>
-    <col min="13" max="13" width="51" customWidth="1"/>
+    <col min="1" max="2" width="27.28515625" customWidth="1"/>
+    <col min="3" max="3" width="37.85546875" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="9" max="9" width="79" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="45.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="83.42578125" customWidth="1"/>
+    <col min="12" max="12" width="62.42578125" customWidth="1"/>
+    <col min="13" max="13" width="55.85546875" customWidth="1"/>
+    <col min="14" max="14" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>10</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="B2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="19">
+      <c r="E2" s="19">
         <v>2</v>
       </c>
-      <c r="E2" s="9">
+      <c r="F2" s="9">
         <v>30.75</v>
       </c>
-      <c r="F2" s="9">
-        <f>D2*E2</f>
+      <c r="G2" s="9">
+        <f>E2*F2</f>
         <v>61.5</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="5"/>
+      <c r="I2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="2"/>
-    </row>
-    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K2" s="2"/>
+    </row>
+    <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="19">
+        <v>1</v>
+      </c>
+      <c r="F3" s="9">
+        <v>8.51</v>
+      </c>
+      <c r="G3" s="9">
+        <f>E3*F3</f>
+        <v>8.51</v>
+      </c>
+      <c r="H3" s="5"/>
+      <c r="I3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J3" s="1"/>
+    </row>
+    <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D3" s="19">
+      <c r="E4" s="19">
+        <v>2</v>
+      </c>
+      <c r="F4" s="9">
+        <v>11.25</v>
+      </c>
+      <c r="G4" s="9">
+        <f t="shared" ref="G4" si="0">E4*F4</f>
+        <v>22.5</v>
+      </c>
+      <c r="H4" s="5"/>
+      <c r="I4" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="J4" s="4"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+    </row>
+    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" s="19">
+        <v>2</v>
+      </c>
+      <c r="F5" s="9">
+        <v>14</v>
+      </c>
+      <c r="G5" s="9">
+        <f t="shared" ref="G5" si="1">E5*F5</f>
+        <v>28</v>
+      </c>
+      <c r="H5" s="5"/>
+      <c r="I5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J5" s="4"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+    </row>
+    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="2">
+        <v>2</v>
+      </c>
+      <c r="F6" s="9">
+        <v>2.72</v>
+      </c>
+      <c r="G6" s="9">
+        <f>F6*E6</f>
+        <v>5.44</v>
+      </c>
+      <c r="H6" s="5"/>
+      <c r="I6" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="2">
         <v>1</v>
       </c>
-      <c r="E3" s="9">
-        <v>8.51</v>
-      </c>
-      <c r="F3" s="9">
-        <f>D3*E3</f>
-        <v>8.51</v>
-      </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I3" s="1"/>
-    </row>
-    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="19">
-        <v>2</v>
-      </c>
-      <c r="E4" s="9">
-        <v>11.21</v>
-      </c>
-      <c r="F4" s="9">
-        <f t="shared" ref="F4:F6" si="0">D4*E4</f>
-        <v>22.42</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" s="4"/>
-    </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" s="19">
-        <v>2</v>
-      </c>
-      <c r="E5" s="9">
-        <v>11.25</v>
-      </c>
-      <c r="F5" s="9">
-        <f t="shared" ref="F5" si="1">D5*E5</f>
-        <v>22.5</v>
-      </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-    </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="F7" s="9">
+        <v>12.54</v>
+      </c>
+      <c r="G7" s="9">
+        <f t="shared" ref="G7:G11" si="2">F7*E7</f>
+        <v>12.54</v>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="I7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="19">
-        <v>2</v>
-      </c>
-      <c r="E6" s="9">
-        <v>14</v>
-      </c>
-      <c r="F6" s="9">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I6" s="4"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-    </row>
-    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="2">
-        <v>2</v>
-      </c>
-      <c r="E7" s="9">
-        <v>2.72</v>
-      </c>
-      <c r="F7" s="9">
-        <f>E7*D7</f>
-        <v>5.44</v>
-      </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="20" t="s">
+      <c r="D8" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="2">
+      <c r="E8" s="2">
         <v>1</v>
       </c>
-      <c r="E8" s="9">
+      <c r="F8" s="9">
         <v>12.54</v>
       </c>
-      <c r="F8" s="9">
-        <f t="shared" ref="F8:F10" si="2">E8*D8</f>
-        <v>12.54</v>
-      </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="2">
-        <v>1</v>
-      </c>
-      <c r="E9" s="9">
-        <v>12.54</v>
-      </c>
-      <c r="F9" s="9">
+      <c r="G8" s="9">
         <f t="shared" si="2"/>
         <v>12.54</v>
       </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="1" t="s">
+      <c r="H8" s="5"/>
+      <c r="I8" s="1" t="s">
         <v>30</v>
       </c>
+      <c r="J8" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
+      <c r="F9" s="9">
+        <v>128.19</v>
+      </c>
+      <c r="G9" s="9">
+        <f t="shared" si="2"/>
+        <v>128.19</v>
+      </c>
+      <c r="H9" s="5"/>
       <c r="I9" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J9" s="4"/>
+    </row>
+    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="2">
+        <v>5</v>
+      </c>
+      <c r="F10" s="9">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="G10" s="9">
+        <f t="shared" si="2"/>
+        <v>22.400000000000002</v>
+      </c>
+      <c r="H10" s="5"/>
+      <c r="I10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J10" s="4"/>
+    </row>
+    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="2">
+        <v>5</v>
+      </c>
+      <c r="F11" s="9">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="G11" s="9">
+        <f t="shared" si="2"/>
+        <v>22.400000000000002</v>
+      </c>
+      <c r="H11" s="5"/>
+      <c r="I11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J11" s="4"/>
+    </row>
+    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B12" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="D12" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="2">
+      <c r="E12" s="2">
         <v>1</v>
       </c>
-      <c r="E10" s="9">
-        <v>128.19</v>
-      </c>
-      <c r="F10" s="9">
-        <f t="shared" si="2"/>
-        <v>128.19</v>
-      </c>
-      <c r="G10" s="5"/>
-      <c r="H10" s="1" t="s">
+      <c r="F12" s="9">
+        <v>72.62</v>
+      </c>
+      <c r="G12" s="9">
+        <f t="shared" ref="G12:G17" si="3">E12*F12</f>
+        <v>72.62</v>
+      </c>
+      <c r="H12" s="5"/>
+      <c r="I12" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="I10" s="4"/>
-    </row>
-    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="10" t="s">
+      <c r="J12" s="4"/>
+    </row>
+    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B13" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" s="2">
-        <v>1</v>
-      </c>
-      <c r="E11" s="9">
-        <v>72.62</v>
-      </c>
-      <c r="F11" s="9">
-        <f t="shared" ref="F11:F15" si="3">D11*E11</f>
-        <v>72.62</v>
-      </c>
-      <c r="G11" s="5"/>
-      <c r="H11" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I11" s="4"/>
-    </row>
-    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="20">
+      <c r="D13" s="20">
         <v>191930200</v>
       </c>
-      <c r="D12" s="2">
+      <c r="E13" s="2">
         <v>2</v>
       </c>
-      <c r="E12" s="9">
+      <c r="F13" s="9">
         <v>0.5</v>
       </c>
-      <c r="F12" s="9">
+      <c r="G13" s="9">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="G12" s="5"/>
-      <c r="H12" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I12" s="4"/>
-    </row>
-    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" s="16">
+      <c r="H13" s="5"/>
+      <c r="I13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J13" s="4"/>
+    </row>
+    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="16">
         <v>191930089</v>
       </c>
-      <c r="D13" s="2">
+      <c r="E14" s="2">
         <v>2</v>
       </c>
-      <c r="E13" s="9">
+      <c r="F14" s="9">
         <v>0.42</v>
       </c>
-      <c r="F13" s="9">
+      <c r="G14" s="9">
         <f t="shared" si="3"/>
         <v>0.84</v>
       </c>
-      <c r="G13" s="5"/>
-      <c r="H13" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I13" s="4"/>
-    </row>
-    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="2">
+      <c r="H14" s="5"/>
+      <c r="I14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J14" s="4"/>
+    </row>
+    <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="2">
         <v>1</v>
       </c>
-      <c r="E14" s="9">
+      <c r="F15" s="9">
         <v>6.22</v>
       </c>
-      <c r="F14" s="9">
+      <c r="G15" s="9">
         <f t="shared" si="3"/>
         <v>6.22</v>
       </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I14" s="4"/>
-    </row>
-    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="B15" s="2" t="s">
+      <c r="H15" s="5"/>
+      <c r="I15" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1</v>
+      </c>
+      <c r="F16" s="9">
+        <v>12.94</v>
+      </c>
+      <c r="G16" s="9">
+        <f t="shared" si="3"/>
+        <v>12.94</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="J16" s="3"/>
+    </row>
+    <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D15" s="2">
+      <c r="D17" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="2">
         <v>1</v>
       </c>
-      <c r="E15" s="8">
+      <c r="F17" s="8">
         <v>23.22</v>
       </c>
-      <c r="F15" s="9">
+      <c r="G17" s="9">
         <f t="shared" si="3"/>
         <v>23.22</v>
       </c>
-      <c r="G15" s="5"/>
-      <c r="H15" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="I15" s="4"/>
-    </row>
-    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-    </row>
-    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-    </row>
-    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="E20" s="7" t="s">
+      <c r="H17" s="5"/>
+      <c r="I17" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="J17" s="4"/>
+    </row>
+    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+    </row>
+    <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+    </row>
+    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F22" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F20" s="5">
-        <f>SUM(F2:F19)</f>
-        <v>405.53999999999996</v>
+      <c r="G22" s="5">
+        <f>SUM(G2:G21)</f>
+        <v>440.86</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" xr:uid="{47569AE6-6AA0-4875-B93F-ACB3A5943EC4}"/>
-    <hyperlink ref="H4" r:id="rId2" xr:uid="{C0E6E945-7E03-425E-862B-42F2D3A430D7}"/>
-    <hyperlink ref="H10" r:id="rId3" xr:uid="{29C65987-503D-4D38-A3A8-F300B92B5979}"/>
-    <hyperlink ref="H7" r:id="rId4" xr:uid="{D49830EC-B643-4C9C-A66A-316B6E8D393B}"/>
-    <hyperlink ref="H8" r:id="rId5" xr:uid="{DB6CFF9E-0CFE-4630-97DC-2259E72BBA6B}"/>
-    <hyperlink ref="H9" r:id="rId6" xr:uid="{7F0A5667-B170-4E9F-A116-7812C5481D5D}"/>
-    <hyperlink ref="I8" r:id="rId7" xr:uid="{47AB98CE-DF5D-4668-ABC4-20DA7A425CBD}"/>
-    <hyperlink ref="I9" r:id="rId8" xr:uid="{FE305D2A-720D-4EAC-A689-433507294DC8}"/>
-    <hyperlink ref="H11" r:id="rId9" xr:uid="{4AF02486-862F-4C90-B472-12C65FB0F86D}"/>
-    <hyperlink ref="H12" r:id="rId10" xr:uid="{60DC3860-834C-416B-A80D-912D2A7218E7}"/>
-    <hyperlink ref="H13" r:id="rId11" xr:uid="{DEEF517E-6B30-41FE-90B5-BDD5F67AF727}"/>
-    <hyperlink ref="H14" r:id="rId12" xr:uid="{F28C2672-213B-4C58-924E-5743A03E60B9}"/>
-    <hyperlink ref="H6" r:id="rId13" xr:uid="{0BF14A02-DB2B-44C8-ADFD-F6B888D0D1E2}"/>
-    <hyperlink ref="H3" r:id="rId14" xr:uid="{D098FC55-60BA-44A1-88B5-F7A95F7F2234}"/>
-    <hyperlink ref="H5" r:id="rId15" xr:uid="{E4B64C1A-2E26-4C6F-9252-C15670A96A6B}"/>
-    <hyperlink ref="H15" r:id="rId16" xr:uid="{BC482846-CA0B-4C8C-A6F1-3CDFDF09F63D}"/>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{47569AE6-6AA0-4875-B93F-ACB3A5943EC4}"/>
+    <hyperlink ref="I9" r:id="rId2" xr:uid="{29C65987-503D-4D38-A3A8-F300B92B5979}"/>
+    <hyperlink ref="I6" r:id="rId3" xr:uid="{D49830EC-B643-4C9C-A66A-316B6E8D393B}"/>
+    <hyperlink ref="J7" r:id="rId4" xr:uid="{DB6CFF9E-0CFE-4630-97DC-2259E72BBA6B}"/>
+    <hyperlink ref="J8" r:id="rId5" xr:uid="{7F0A5667-B170-4E9F-A116-7812C5481D5D}"/>
+    <hyperlink ref="I7" r:id="rId6" xr:uid="{47AB98CE-DF5D-4668-ABC4-20DA7A425CBD}"/>
+    <hyperlink ref="I8" r:id="rId7" xr:uid="{FE305D2A-720D-4EAC-A689-433507294DC8}"/>
+    <hyperlink ref="I12" r:id="rId8" xr:uid="{4AF02486-862F-4C90-B472-12C65FB0F86D}"/>
+    <hyperlink ref="I13" r:id="rId9" xr:uid="{60DC3860-834C-416B-A80D-912D2A7218E7}"/>
+    <hyperlink ref="I14" r:id="rId10" xr:uid="{DEEF517E-6B30-41FE-90B5-BDD5F67AF727}"/>
+    <hyperlink ref="I15" r:id="rId11" xr:uid="{F28C2672-213B-4C58-924E-5743A03E60B9}"/>
+    <hyperlink ref="I5" r:id="rId12" xr:uid="{0BF14A02-DB2B-44C8-ADFD-F6B888D0D1E2}"/>
+    <hyperlink ref="I3" r:id="rId13" xr:uid="{D098FC55-60BA-44A1-88B5-F7A95F7F2234}"/>
+    <hyperlink ref="I4" r:id="rId14" xr:uid="{E4B64C1A-2E26-4C6F-9252-C15670A96A6B}"/>
+    <hyperlink ref="I17" r:id="rId15" xr:uid="{BC482846-CA0B-4C8C-A6F1-3CDFDF09F63D}"/>
+    <hyperlink ref="I16" r:id="rId16" xr:uid="{33EA6662-3BF5-4567-9053-50ED0DB9E78A}"/>
+    <hyperlink ref="I10" r:id="rId17" xr:uid="{481207C2-2276-4195-833B-5B8F0CF49279}"/>
+    <hyperlink ref="I11" r:id="rId18" xr:uid="{9A6ACCBE-7885-4833-B391-4A619D41B841}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId17"/>
+  <pageSetup orientation="portrait" r:id="rId19"/>
 </worksheet>
 </file>
--- a/accessories/cable-5/cable-5.xlsx
+++ b/accessories/cable-5/cable-5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Battery-Lab-Hardware\accessories\cable-5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A797BD0-3845-4126-BB8E-2335E24DF764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57C98790-A67B-49E1-9A13-ABEE44CB8DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-12765" windowWidth="16440" windowHeight="28320" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>

--- a/accessories/cable-5/cable-5.xlsx
+++ b/accessories/cable-5/cable-5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Battery-Lab-Hardware\accessories\cable-5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57C98790-A67B-49E1-9A13-ABEE44CB8DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F5297E4-A416-497A-BAE8-D7D76C842CC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="28680" yWindow="-150" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -282,7 +282,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -329,6 +329,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -362,7 +379,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -421,6 +438,23 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="7" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1118,30 +1152,30 @@
       <c r="J11" s="4"/>
     </row>
     <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="24">
         <v>1</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="26">
         <v>72.62</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="26">
         <f t="shared" ref="G12:G17" si="3">E12*F12</f>
         <v>72.62</v>
       </c>
-      <c r="H12" s="5"/>
-      <c r="I12" s="1" t="s">
+      <c r="H12" s="27"/>
+      <c r="I12" s="28" t="s">
         <v>38</v>
       </c>
       <c r="J12" s="4"/>
@@ -1208,8 +1242,8 @@
       <c r="A15" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="17" t="s">
-        <v>66</v>
+      <c r="B15" s="10" t="s">
+        <v>67</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>46</v>
@@ -1236,8 +1270,8 @@
       <c r="A16" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>67</v>
+      <c r="B16" s="17" t="s">
+        <v>66</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>68</v>

--- a/accessories/cable-5/cable-5.xlsx
+++ b/accessories/cable-5/cable-5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Battery-Lab-Hardware\accessories\cable-5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F5297E4-A416-497A-BAE8-D7D76C842CC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA7B6861-B2D8-4218-B4F2-A9CC84728C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-150" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
@@ -282,7 +282,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -337,15 +337,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <strike/>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -379,7 +370,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -454,7 +445,6 @@
     <xf numFmtId="7" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1175,7 +1165,7 @@
         <v>72.62</v>
       </c>
       <c r="H12" s="27"/>
-      <c r="I12" s="28" t="s">
+      <c r="I12" s="1" t="s">
         <v>38</v>
       </c>
       <c r="J12" s="4"/>
